--- a/other/input/wqx_templates/wqx_template_matching_table.xlsx
+++ b/other/input/wqx_templates/wqx_template_matching_table.xlsx
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="226">
   <si>
     <t>KR RM 0 NNC</t>
   </si>
@@ -717,6 +717,12 @@
   </si>
   <si>
     <t xml:space="preserve">Weak Acid Diss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-150.636905</t>
   </si>
 </sst>
 </file>
@@ -741,8 +747,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
       <b/>
     </font>
   </fonts>
@@ -1294,7 +1298,7 @@
         <v>60.489843999999998</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>44</v>
+        <v>225</v>
       </c>
       <c r="C16" t="s">
         <v>28</v>
@@ -2282,7 +2286,7 @@
         <v>117</v>
       </c>
       <c r="B5" t="s">
-        <v>123</v>
+        <v>224</v>
       </c>
       <c r="C5" t="s">
         <v>92</v>

--- a/other/input/wqx_templates/wqx_template_matching_table.xlsx
+++ b/other/input/wqx_templates/wqx_template_matching_table.xlsx
@@ -13,17 +13,16 @@
     <sheet name="chemical_preservative" sheetId="4" state="visible" r:id="rId5"/>
     <sheet name="sample_container_type_color" sheetId="5" state="visible" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
-<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" mc:Ignorable="xr">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
+    <comment ref="A1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -728,8 +727,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <fonts count="3">
     <font>
       <sz val="11"/>
@@ -797,7 +795,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1407,7 +1404,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
@@ -1698,8 +1695,10 @@
       <c r="B20" t="s">
         <v>33</v>
       </c>
-      <c r="C20" t="s">
-        <v>144</v>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>KBL_m_50.0</t>
+        </is>
       </c>
       <c r="D20" t="s">
         <v>167</v>
@@ -1712,8 +1711,10 @@
       <c r="B21" t="s">
         <v>37</v>
       </c>
-      <c r="C21" t="s">
-        <v>146</v>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>KBL_m_70.0</t>
+        </is>
       </c>
       <c r="D21" t="s">
         <v>168</v>
@@ -1749,7 +1750,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
@@ -1777,64 +1778,46 @@
       <c r="A2" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="B2"/>
-      <c r="C2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
         <v>178</v>
       </c>
-      <c r="B3"/>
-      <c r="C3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
         <v>179</v>
       </c>
-      <c r="B4"/>
-      <c r="C4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
         <v>180</v>
       </c>
-      <c r="B5"/>
-      <c r="C5"/>
     </row>
     <row r="6">
       <c r="A6" t="s">
         <v>181</v>
       </c>
-      <c r="B6"/>
-      <c r="C6"/>
     </row>
     <row r="7">
       <c r="A7" t="s">
         <v>182</v>
       </c>
-      <c r="B7"/>
-      <c r="C7"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
         <v>183</v>
       </c>
-      <c r="B8"/>
-      <c r="C8"/>
     </row>
     <row r="9">
       <c r="A9" t="s">
         <v>184</v>
       </c>
-      <c r="B9"/>
-      <c r="C9"/>
     </row>
     <row r="10">
       <c r="A10" t="s">
         <v>185</v>
       </c>
-      <c r="B10"/>
-      <c r="C10"/>
     </row>
     <row r="11">
       <c r="A11" t="s">
@@ -1851,113 +1834,81 @@
       <c r="A12" t="s">
         <v>188</v>
       </c>
-      <c r="B12"/>
-      <c r="C12"/>
     </row>
     <row r="13">
       <c r="A13" t="s">
         <v>189</v>
       </c>
-      <c r="B13"/>
-      <c r="C13"/>
     </row>
     <row r="14">
       <c r="A14" t="s">
         <v>190</v>
       </c>
-      <c r="B14"/>
-      <c r="C14"/>
     </row>
     <row r="15">
       <c r="A15" t="s">
         <v>191</v>
       </c>
-      <c r="B15"/>
-      <c r="C15"/>
     </row>
     <row r="16">
       <c r="A16" t="s">
         <v>192</v>
       </c>
-      <c r="B16"/>
-      <c r="C16"/>
     </row>
     <row r="17">
       <c r="A17" t="s">
         <v>193</v>
       </c>
-      <c r="B17"/>
-      <c r="C17"/>
     </row>
     <row r="18">
       <c r="A18" t="s">
         <v>194</v>
       </c>
-      <c r="B18"/>
-      <c r="C18"/>
     </row>
     <row r="19">
       <c r="A19" t="s">
         <v>195</v>
       </c>
-      <c r="B19"/>
-      <c r="C19"/>
     </row>
     <row r="20">
       <c r="A20" t="s">
         <v>196</v>
       </c>
-      <c r="B20"/>
-      <c r="C20"/>
     </row>
     <row r="21">
       <c r="A21" t="s">
         <v>197</v>
       </c>
-      <c r="B21"/>
-      <c r="C21"/>
     </row>
     <row r="22">
       <c r="A22" t="s">
         <v>198</v>
       </c>
-      <c r="B22"/>
-      <c r="C22"/>
     </row>
     <row r="23">
       <c r="A23" t="s">
         <v>199</v>
       </c>
-      <c r="B23"/>
-      <c r="C23"/>
     </row>
     <row r="24">
       <c r="A24" t="s">
         <v>200</v>
       </c>
-      <c r="B24"/>
-      <c r="C24"/>
     </row>
     <row r="25">
       <c r="A25" t="s">
         <v>201</v>
       </c>
-      <c r="B25"/>
-      <c r="C25"/>
     </row>
     <row r="26">
       <c r="A26" t="s">
         <v>202</v>
       </c>
-      <c r="B26"/>
-      <c r="C26"/>
     </row>
     <row r="27">
       <c r="A27" t="s">
         <v>203</v>
       </c>
-      <c r="B27"/>
-      <c r="C27"/>
     </row>
     <row r="28">
       <c r="A28" t="s">
@@ -1996,22 +1947,16 @@
       <c r="A31" t="s">
         <v>212</v>
       </c>
-      <c r="B31"/>
-      <c r="C31"/>
     </row>
     <row r="32">
       <c r="A32" t="s">
         <v>213</v>
       </c>
-      <c r="B32"/>
-      <c r="C32"/>
     </row>
     <row r="33">
       <c r="A33" t="s">
         <v>214</v>
       </c>
-      <c r="B33"/>
-      <c r="C33"/>
     </row>
     <row r="34">
       <c r="A34" t="s">
@@ -2028,15 +1973,11 @@
       <c r="A35" t="s">
         <v>218</v>
       </c>
-      <c r="B35"/>
-      <c r="C35"/>
     </row>
     <row r="36">
       <c r="A36" t="s">
         <v>219</v>
       </c>
-      <c r="B36"/>
-      <c r="C36"/>
     </row>
     <row r="37">
       <c r="A37" t="s">
@@ -2053,12 +1994,10 @@
       <c r="A38" t="s">
         <v>223</v>
       </c>
-      <c r="B38"/>
-      <c r="C38"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <legacyDrawing r:id="rIdvml"/>
 </worksheet>
 </file>
@@ -2122,7 +2061,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
@@ -2211,7 +2150,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
@@ -2344,6 +2283,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>